--- a/02_加值成品/生物/生物6-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/生物/生物6-2_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國一(七年級) 生物6-2 性別決定與人類遺傳　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國一(七年級) 生物6-2 性別決定與人類遺傳　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>人類有幾對染色體？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>決定性別與部分性聯性狀</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>性聯隱性只需一個X上隱性即表現</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>23對</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>46條</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>女性的性染色體是？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>性染色體</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>一X一Y</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>性聯遺傳</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>XX</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>女</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>男性的性染色體是？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>XY</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>父親</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>男性</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>一X一Y</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>男</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>子女性別由誰決定？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>只有一個X</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>性染色體</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>一X一Y</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>父親</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>X或Y</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>父親提供X生的是？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>父親</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>女兒</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>XX</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>性聯遺傳</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>父親提供Y生的是？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>兒子</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>只有一個X</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>XY</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>性染色體</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>Y</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>與性染色體相關的遺傳稱？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>只有一個X</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>性聯遺傳</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>XY</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>性聯</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>色盲較常見於？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>男性</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>XX</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>X染色體</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>XY</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>性聯</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>決定人類性別的是哪對染色體？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>兒子</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>XY</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>性染色體</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>女兒</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>第23對</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>女性的兩條性染色體都是？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>女兒</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>兒子</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>XY</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>XX</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國一(七年級) 生物6-2 性別決定與人類遺傳　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國一(七年級) 生物6-2 性別決定與人類遺傳　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>人類體染色體有幾對？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>女兒</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>一條來自母一條來自父</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>22對</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>決定性別的基因異常</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>非性染色體</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>性別決定由哪對染色體？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>兒子</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>性染色體</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>XX</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>男性</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>第23對</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>母親提供的性染色體一定是？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>男性</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>X染色體</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>性聯遺傳</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>XX</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>為何生男生女機率約各半？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>父親X、Y各半</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>隱性基因在X上依性別表現不同</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>母提供X父提供X或Y,Y為男X為女</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>一條來自母一條來自父</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>機率</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>性聯遺傳男性較易表現因為？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>女兒</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>父親</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>兒子</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>只有一個X</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>單X</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>血友病屬哪類遺傳？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>父親</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>性聯遺傳</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>XX</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>兒子</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>X相關</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>人類染色體共幾條？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>兒子</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>隱性基因在X上依性別表現不同</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>46條</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>23對</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>XY是男還女？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>XX</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>X染色體</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>女兒</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>男性</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>XY</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>男性的性染色體組成為？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>性聯遺傳</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>XY</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>一X一Y</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>女兒</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>XY</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>性聯遺傳的基因多位於哪條染色體？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>X染色體</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>女兒</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>男性</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>一X一Y</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>性聯</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國一(七年級) 生物6-2 性別決定與人類遺傳　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國一(七年級) 生物6-2 性別決定與人類遺傳　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>說明子女性別如何由父親決定？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>母提供X父提供X或Y,Y為男X為女</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>隱性基因在X上依性別表現不同</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>性聯隱性只需一個X上隱性即表現</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>父親X、Y各半</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>決定</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>為何色盲血友病男性較常見？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>性聯隱性只需一個X上隱性即表現</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>一條來自母一條來自父</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>父親X、Y各半</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>隱性基因在X上依性別表現不同</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>性聯</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>生男生女機率約各半的原因？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>一條來自母一條來自父</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>決定性別的基因異常</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>性染色體決定性別、體染色體其他性狀</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>父親精子帶X或Y約各半</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>機率</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>性染色體與體染色體的差別？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>父親精子帶X或Y約各半</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>一條來自母一條來自父</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>性染色體決定性別、體染色體其他性狀</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>父親X、Y各半</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>區別</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>母親為色盲帶因者對兒子的影響？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>決定性別與部分性聯性狀</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>母提供X父提供X或Y,Y為男X為女</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>父親精子帶X或Y約各半</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>兒子有較高機率色盲</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>遺傳</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>人類23對染色體中性染色體的角色？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>決定性別的基因異常</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>一條來自母一條來自父</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>父親精子帶X或Y約各半</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>決定性別與部分性聯性狀</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>角色</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>性聯遺傳為何常隔代或偏一性別？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>一條來自母一條來自父</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>決定性別與部分性聯性狀</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>兒子有較高機率色盲</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>隱性基因在X上依性別表現不同</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>模式</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>遺傳諮詢對遺傳疾病的意義？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>評估風險協助預防</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>一條來自母一條來自父</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>兒子有較高機率色盲</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>父親X、Y各半</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>應用</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>女兒的兩條X染色體分別來自？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>父親精子帶X或Y約各半</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>性聯隱性只需一個X上隱性即表現</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>兒子有較高機率色盲</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>一條來自母一條來自父</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>來源</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>為何性染色體異常可能影響性別發育？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>性聯隱性只需一個X上隱性即表現</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>決定性別與部分性聯性狀</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>評估風險協助預防</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>決定性別的基因異常</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>異常</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/生物/生物6-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/生物/生物6-2_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>46條</t>
+          <t>23對染色體：人體細胞裡的染色體共有23對,合起來就是46條</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>女</t>
+          <t>女性為XX：女生的第23對性染色體是兩條X,所以寫成XX</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>男</t>
+          <t>男性為XY：男生的第23對性染色體是一條X一條Y,所以寫成XY</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>X或Y</t>
+          <t>父親決定：母親只能給X,父親能給X或Y,所以性別由父親提供的染色體決定</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>生女：父親若提供X,和母親的X配成XX,寶寶就是女生</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>生男：父親若提供Y,和母親的X配成XY,寶寶就是男生</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>性聯</t>
+          <t>性聯遺傳：像色盲這類疾病的基因就在性染色體上,這種遺傳方式叫性聯遺傳</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>性聯</t>
+          <t>男性較多：男生只有一個X,只要那個X帶色盲基因就會表現出來,所以男生較常見</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>第23對</t>
+          <t>第23對：人類共23對染色體，其中最後一對（第23對）是性染色體，決定個體的性別</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>XX</t>
+          <t>XX：女性的性染色體組成是兩條X染色體，寫成XX</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>非性染色體</t>
+          <t>22對體染色體：23對染色體中,除了1對性染色體,其餘22對是決定其他性狀的體染色體</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>第23對</t>
+          <t>第23對：23對染色體中的最後一對就是性染色體,負責決定男女性別</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>XX</t>
+          <t>母親只有X：女性的性染色體是XX,不管給哪一條,提供的一定是X</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>機率</t>
+          <t>機率各半：父親的精子帶X或帶Y的數量差不多相等,所以生男生女機率各約一半</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>單X</t>
+          <t>只有一個X：男生只有一條X染色體,上面的隱性基因沒有另一條X可以遮蓋,就會表現出來</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>X相關</t>
+          <t>性聯遺傳：血友病的基因位在X染色體上,屬於性聯遺傳,男性較容易罹患</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>23對</t>
+          <t>46條：人體細胞內的染色體是23對,每對2條,合計共有46條</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>XY</t>
+          <t>男性：性染色體組成是XY,一條X一條Y,代表這是男生</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>XY</t>
+          <t>XY：男性的性染色體組成是一條X染色體和一條Y染色體，寫成XY</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>性聯</t>
+          <t>性聯：許多性聯遺傳的疾病基因位於X染色體上，因此遺傳表現常和性別有關</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>決定</t>
+          <t>父親決定性別：母親一定提供X,父親若提供X會生女兒,若提供Y則會生兒子</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>性聯</t>
+          <t>單X易顯現：男生只有一條X,只要這條X帶隱性致病基因就會發病,不像女生有第二條X可能遮蓋</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>機率</t>
+          <t>精子比例相近：父親製造的精子中帶X和帶Y的數量大約相等,所以生男生女的機率也各約一半</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>區別</t>
+          <t>分工不同：性染色體那一對專門決定男女性別,其餘22對體染色體則決定身高膚色等其他性狀</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>遺傳</t>
+          <t>較高風險：兒子只有一條X,若剛好接到母親帶色盲基因的那條X,就會表現出色盲</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>角色</t>
+          <t>決定性別與性狀：第23對性染色體不只決定男女,也帶有色盲等性聯性狀的基因</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>模式</t>
+          <t>依性別表現：隱性基因在X染色體上,女生有兩條X較易被遮蓋,男生只有一條容易顯現,所以常偏向某一性別出現</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>應用</t>
+          <t>評估與預防：遺傳諮詢可以幫助家庭了解生下遺傳疾病寶寶的機率,提早做準備或預防</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>來源</t>
+          <t>來源：女兒的性染色體是XX，其中一條X來自母親，另一條X則來自父親（父親唯一的X染色體）</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>異常</t>
+          <t>異常：性染色體上帶有決定性別發育的重要基因，若性染色體數目或結構異常，可能干擾這些基因的正常表現，進而影響性別發育</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/生物/生物6-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/生物/生物6-2_三種難度測驗卷.xlsx
@@ -563,17 +563,17 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>46條</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>決定性別與部分性聯性狀</t>
+          <t>性聯遺傳</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>性聯隱性只需一個X上隱性即表現</t>
+          <t>XY</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -603,17 +603,17 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>性染色體</t>
+          <t>一X一Y</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>一X一Y</t>
+          <t>女兒</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>性聯遺傳</t>
+          <t>兒子</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
@@ -648,17 +648,17 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>父親</t>
+          <t>性染色體</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>男性</t>
+          <t>兒子</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>一X一Y</t>
+          <t>女兒</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -923,12 +923,12 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>女兒</t>
+          <t>兒子</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>兒子</t>
+          <t>性聯遺傳</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>XY</t>
+          <t>男性</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>一條來自母一條來自父</t>
+          <t>父親</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>決定性別的基因異常</t>
+          <t>XX</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -1124,17 +1124,17 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>男性</t>
+          <t>性染色體</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>X染色體</t>
+          <t>兒子</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>性聯遺傳</t>
+          <t>父親</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>父親</t>
+          <t>XY</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>兒子</t>
+          <t>性染色體</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>隱性基因在X上依性別表現不同</t>
+          <t>23對</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>父親</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -1359,12 +1359,12 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>性聯遺傳</t>
+          <t>男性</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>XY</t>
+          <t>XX</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>女兒</t>
+          <t>父親</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -1404,17 +1404,17 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>女兒</t>
+          <t>兒子</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>男性</t>
+          <t>XX</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>一X一Y</t>
+          <t>只有一個X</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
